--- a/backend/data/financials_by_company/0769.HK.xlsx
+++ b/backend/data/financials_by_company/0769.HK.xlsx
@@ -667,56 +667,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-4392750</v>
+        <v>-631705.800662</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.09425600000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>-59790000</v>
+        <v>70878000</v>
       </c>
       <c r="E2" t="n">
-        <v>-17571000</v>
+        <v>-6702000</v>
       </c>
       <c r="F2" t="n">
-        <v>-17571000</v>
+        <v>-6702000</v>
       </c>
       <c r="G2" t="n">
-        <v>-104924000</v>
+        <v>24274000</v>
       </c>
       <c r="H2" t="n">
-        <v>29174000</v>
+        <v>35638000</v>
       </c>
       <c r="I2" t="n">
-        <v>809646000</v>
+        <v>1126488000</v>
       </c>
       <c r="J2" t="n">
-        <v>-77361000</v>
+        <v>64176000</v>
       </c>
       <c r="K2" t="n">
-        <v>-106535000</v>
+        <v>28538000</v>
       </c>
       <c r="L2" t="n">
-        <v>-42000</v>
+        <v>5401000</v>
       </c>
       <c r="M2" t="n">
-        <v>42000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>455000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5856000</v>
+      </c>
       <c r="O2" t="n">
-        <v>-91745750</v>
+        <v>30344294.199338</v>
       </c>
       <c r="P2" t="n">
-        <v>-104924000</v>
+        <v>24274000</v>
       </c>
       <c r="Q2" t="n">
-        <v>846076000</v>
+        <v>1184189000</v>
       </c>
       <c r="R2" t="n">
-        <v>-106535000</v>
+        <v>28538000</v>
       </c>
       <c r="S2" t="n">
         <v>2341700000</v>
@@ -725,143 +727,143 @@
         <v>2341700000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0448</v>
+        <v>0.0104</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0448</v>
+        <v>0.0104</v>
       </c>
       <c r="W2" t="n">
-        <v>-104924000</v>
+        <v>24274000</v>
       </c>
       <c r="X2" t="n">
-        <v>-104924000</v>
+        <v>24274000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-104924000</v>
+        <v>24274000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2222000</v>
+        <v>-1162000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-107146000</v>
+        <v>25436000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-107146000</v>
+        <v>25436000</v>
       </c>
       <c r="AD2" t="n">
-        <v>569000</v>
+        <v>2647000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-106577000</v>
+        <v>28083000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2007000</v>
+        <v>-747000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-17571000</v>
+        <v>-6702000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-294000</v>
+        <v>-491000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3967000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>21832000</v>
-      </c>
+        <v>7193000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-42000</v>
+        <v>5401000</v>
       </c>
       <c r="AL2" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>455000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5856000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>-89419000</v>
+        <v>28282000</v>
       </c>
       <c r="AO2" t="n">
-        <v>36430000</v>
+        <v>57701000</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>36430000</v>
+        <v>57701000</v>
       </c>
       <c r="AR2" t="n">
-        <v>4922000</v>
+        <v>13230000</v>
       </c>
       <c r="AS2" t="n">
-        <v>31508000</v>
+        <v>44471000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-52989000</v>
+        <v>85983000</v>
       </c>
       <c r="AU2" t="n">
-        <v>809646000</v>
+        <v>1126488000</v>
       </c>
       <c r="AV2" t="n">
-        <v>756657000</v>
+        <v>1212471000</v>
       </c>
       <c r="AW2" t="n">
-        <v>756657000</v>
+        <v>1212471000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2074.070373</v>
+        <v>-3722750</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002669</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-176735000</v>
+        <v>-338463000</v>
       </c>
       <c r="E3" t="n">
-        <v>777000</v>
+        <v>-14891000</v>
       </c>
       <c r="F3" t="n">
-        <v>777000</v>
+        <v>-14891000</v>
       </c>
       <c r="G3" t="n">
-        <v>-200545000</v>
+        <v>-373296000</v>
       </c>
       <c r="H3" t="n">
-        <v>33898000</v>
+        <v>38295000</v>
       </c>
       <c r="I3" t="n">
-        <v>837388000</v>
+        <v>809297000</v>
       </c>
       <c r="J3" t="n">
-        <v>-175958000</v>
+        <v>-353354000</v>
       </c>
       <c r="K3" t="n">
-        <v>-209856000</v>
+        <v>-391649000</v>
       </c>
       <c r="L3" t="n">
-        <v>-309000</v>
+        <v>4575000</v>
       </c>
       <c r="M3" t="n">
-        <v>309000</v>
+        <v>297000</v>
       </c>
       <c r="N3" t="n">
-        <v>2862000</v>
+        <v>4872000</v>
       </c>
       <c r="O3" t="n">
-        <v>-201319925.929627</v>
+        <v>-362127750</v>
       </c>
       <c r="P3" t="n">
-        <v>-200545000</v>
+        <v>-373296000</v>
       </c>
       <c r="Q3" t="n">
-        <v>893246000</v>
+        <v>1184270000</v>
       </c>
       <c r="R3" t="n">
-        <v>-209856000</v>
+        <v>-391649000</v>
       </c>
       <c r="S3" t="n">
         <v>2341700000</v>
@@ -870,145 +872,145 @@
         <v>2341700000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0856</v>
+        <v>-0.1594</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0856</v>
+        <v>-0.1594</v>
       </c>
       <c r="W3" t="n">
-        <v>-200545000</v>
+        <v>-373296000</v>
       </c>
       <c r="X3" t="n">
-        <v>-200545000</v>
+        <v>-373296000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-200545000</v>
+        <v>-373296000</v>
       </c>
       <c r="AA3" t="n">
-        <v>9059000</v>
+        <v>20381000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-209604000</v>
+        <v>-393677000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-209604000</v>
+        <v>-393677000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-561000</v>
+        <v>1731000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-210165000</v>
+        <v>-391946000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-4071000</v>
+        <v>152000</v>
       </c>
       <c r="AG3" t="n">
-        <v>777000</v>
+        <v>-14891000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-5719000</v>
+        <v>-397000</v>
       </c>
       <c r="AI3" t="n">
-        <v>4942000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
+        <v>15288000</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-309000</v>
+        <v>4575000</v>
       </c>
       <c r="AL3" t="n">
-        <v>309000</v>
+        <v>297000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2862000</v>
+        <v>4872000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-207173000</v>
+        <v>-373857000</v>
       </c>
       <c r="AO3" t="n">
-        <v>55858000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>374973000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>326412000</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>55858000</v>
+        <v>48609000</v>
       </c>
       <c r="AR3" t="n">
-        <v>9823000</v>
+        <v>11815000</v>
       </c>
       <c r="AS3" t="n">
-        <v>46035000</v>
+        <v>36794000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-151315000</v>
+        <v>1116000</v>
       </c>
       <c r="AU3" t="n">
-        <v>837388000</v>
+        <v>809297000</v>
       </c>
       <c r="AV3" t="n">
-        <v>686073000</v>
+        <v>810413000</v>
       </c>
       <c r="AW3" t="n">
-        <v>686073000</v>
+        <v>810413000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3722750</v>
+        <v>2074.070373</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.002669</v>
       </c>
       <c r="D4" t="n">
-        <v>-338463000</v>
+        <v>-176735000</v>
       </c>
       <c r="E4" t="n">
-        <v>-14891000</v>
+        <v>777000</v>
       </c>
       <c r="F4" t="n">
-        <v>-14891000</v>
+        <v>777000</v>
       </c>
       <c r="G4" t="n">
-        <v>-373296000</v>
+        <v>-200545000</v>
       </c>
       <c r="H4" t="n">
-        <v>38295000</v>
+        <v>33898000</v>
       </c>
       <c r="I4" t="n">
-        <v>809297000</v>
+        <v>837388000</v>
       </c>
       <c r="J4" t="n">
-        <v>-353354000</v>
+        <v>-175958000</v>
       </c>
       <c r="K4" t="n">
-        <v>-391649000</v>
+        <v>-209856000</v>
       </c>
       <c r="L4" t="n">
-        <v>4575000</v>
+        <v>-309000</v>
       </c>
       <c r="M4" t="n">
-        <v>297000</v>
+        <v>309000</v>
       </c>
       <c r="N4" t="n">
-        <v>4872000</v>
+        <v>2862000</v>
       </c>
       <c r="O4" t="n">
-        <v>-362127750</v>
+        <v>-201319925.929627</v>
       </c>
       <c r="P4" t="n">
-        <v>-373296000</v>
+        <v>-200545000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1184270000</v>
+        <v>893246000</v>
       </c>
       <c r="R4" t="n">
-        <v>-391649000</v>
+        <v>-209856000</v>
       </c>
       <c r="S4" t="n">
         <v>2341700000</v>
@@ -1017,145 +1019,143 @@
         <v>2341700000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1594</v>
+        <v>-0.0856</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1594</v>
+        <v>-0.0856</v>
       </c>
       <c r="W4" t="n">
-        <v>-373296000</v>
+        <v>-200545000</v>
       </c>
       <c r="X4" t="n">
-        <v>-373296000</v>
+        <v>-200545000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-373296000</v>
+        <v>-200545000</v>
       </c>
       <c r="AA4" t="n">
-        <v>20381000</v>
+        <v>9059000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-393677000</v>
+        <v>-209604000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-393677000</v>
+        <v>-209604000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1731000</v>
+        <v>-561000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-391946000</v>
+        <v>-210165000</v>
       </c>
       <c r="AF4" t="n">
-        <v>152000</v>
+        <v>-4071000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-14891000</v>
+        <v>777000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-397000</v>
+        <v>-5719000</v>
       </c>
       <c r="AI4" t="n">
-        <v>15288000</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>4942000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AK4" t="n">
-        <v>4575000</v>
+        <v>-309000</v>
       </c>
       <c r="AL4" t="n">
-        <v>297000</v>
+        <v>309000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4872000</v>
+        <v>2862000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-373857000</v>
+        <v>-207173000</v>
       </c>
       <c r="AO4" t="n">
-        <v>374973000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>326412000</v>
-      </c>
+        <v>55858000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>48609000</v>
+        <v>55858000</v>
       </c>
       <c r="AR4" t="n">
-        <v>11815000</v>
+        <v>9823000</v>
       </c>
       <c r="AS4" t="n">
-        <v>36794000</v>
+        <v>46035000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1116000</v>
+        <v>-151315000</v>
       </c>
       <c r="AU4" t="n">
-        <v>809297000</v>
+        <v>837388000</v>
       </c>
       <c r="AV4" t="n">
-        <v>810413000</v>
+        <v>686073000</v>
       </c>
       <c r="AW4" t="n">
-        <v>810413000</v>
+        <v>686073000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-631705.800662</v>
+        <v>-4392750</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09425600000000001</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>70878000</v>
+        <v>-59790000</v>
       </c>
       <c r="E5" t="n">
-        <v>-6702000</v>
+        <v>-17571000</v>
       </c>
       <c r="F5" t="n">
-        <v>-6702000</v>
+        <v>-17571000</v>
       </c>
       <c r="G5" t="n">
-        <v>24274000</v>
+        <v>-104924000</v>
       </c>
       <c r="H5" t="n">
-        <v>35638000</v>
+        <v>29174000</v>
       </c>
       <c r="I5" t="n">
-        <v>1126488000</v>
+        <v>809646000</v>
       </c>
       <c r="J5" t="n">
-        <v>64176000</v>
+        <v>-77361000</v>
       </c>
       <c r="K5" t="n">
-        <v>28538000</v>
+        <v>-106535000</v>
       </c>
       <c r="L5" t="n">
-        <v>5401000</v>
+        <v>-42000</v>
       </c>
       <c r="M5" t="n">
-        <v>455000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5856000</v>
-      </c>
+        <v>42000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>30344294.199338</v>
+        <v>-91745750</v>
       </c>
       <c r="P5" t="n">
-        <v>24274000</v>
+        <v>-104924000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1184189000</v>
+        <v>846076000</v>
       </c>
       <c r="R5" t="n">
-        <v>28538000</v>
+        <v>-106535000</v>
       </c>
       <c r="S5" t="n">
         <v>2341700000</v>
@@ -1164,87 +1164,87 @@
         <v>2341700000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0104</v>
+        <v>-0.0448</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0104</v>
+        <v>-0.0448</v>
       </c>
       <c r="W5" t="n">
-        <v>24274000</v>
+        <v>-104924000</v>
       </c>
       <c r="X5" t="n">
-        <v>24274000</v>
+        <v>-104924000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>24274000</v>
+        <v>-104924000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1162000</v>
+        <v>2222000</v>
       </c>
       <c r="AB5" t="n">
-        <v>25436000</v>
+        <v>-107146000</v>
       </c>
       <c r="AC5" t="n">
-        <v>25436000</v>
+        <v>-107146000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2647000</v>
+        <v>569000</v>
       </c>
       <c r="AE5" t="n">
-        <v>28083000</v>
+        <v>-106577000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-747000</v>
+        <v>2007000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-6702000</v>
+        <v>-17571000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-491000</v>
+        <v>-294000</v>
       </c>
       <c r="AI5" t="n">
-        <v>7193000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-3967000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>21832000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>5401000</v>
+        <v>-42000</v>
       </c>
       <c r="AL5" t="n">
-        <v>455000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>5856000</v>
-      </c>
+        <v>42000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>28282000</v>
+        <v>-89419000</v>
       </c>
       <c r="AO5" t="n">
-        <v>57701000</v>
+        <v>36430000</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>57701000</v>
+        <v>36430000</v>
       </c>
       <c r="AR5" t="n">
-        <v>13230000</v>
+        <v>4922000</v>
       </c>
       <c r="AS5" t="n">
-        <v>44471000</v>
+        <v>31508000</v>
       </c>
       <c r="AT5" t="n">
-        <v>85983000</v>
+        <v>-52989000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1126488000</v>
+        <v>809646000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1212471000</v>
+        <v>756657000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1212471000</v>
+        <v>756657000</v>
       </c>
     </row>
   </sheetData>
@@ -1550,50 +1550,50 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>2341700281</v>
+        <v>2341700000</v>
       </c>
       <c r="C2" t="n">
-        <v>2341700281</v>
+        <v>2341700000</v>
       </c>
       <c r="D2" t="n">
-        <v>664000</v>
+        <v>1744000</v>
       </c>
       <c r="E2" t="n">
-        <v>1917361000</v>
+        <v>2881361000</v>
       </c>
       <c r="F2" t="n">
-        <v>1917361000</v>
+        <v>2881361000</v>
       </c>
       <c r="G2" t="n">
-        <v>1730138000</v>
+        <v>2575215000</v>
       </c>
       <c r="H2" t="n">
-        <v>1917361000</v>
+        <v>2881361000</v>
       </c>
       <c r="I2" t="n">
-        <v>664000</v>
+        <v>1744000</v>
       </c>
       <c r="J2" t="n">
-        <v>1917361000</v>
+        <v>2881361000</v>
       </c>
       <c r="K2" t="n">
-        <v>1917361000</v>
+        <v>2881361000</v>
       </c>
       <c r="L2" t="n">
-        <v>1895377000</v>
+        <v>2890248000</v>
       </c>
       <c r="M2" t="n">
-        <v>-21984000</v>
+        <v>8887000</v>
       </c>
       <c r="N2" t="n">
-        <v>1917361000</v>
+        <v>2881361000</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-841954000</v>
+        <v>-179403000</v>
       </c>
       <c r="Q2" t="n">
         <v>2093306000</v>
@@ -1605,46 +1605,46 @@
         <v>234170000</v>
       </c>
       <c r="T2" t="n">
-        <v>107219000</v>
+        <v>156757000</v>
       </c>
       <c r="U2" t="n">
-        <v>230000</v>
+        <v>1391000</v>
       </c>
       <c r="V2" t="n">
-        <v>230000</v>
+        <v>1391000</v>
       </c>
       <c r="W2" t="n">
-        <v>230000</v>
+        <v>1391000</v>
       </c>
       <c r="X2" t="n">
-        <v>106989000</v>
+        <v>155366000</v>
       </c>
       <c r="Y2" t="n">
-        <v>434000</v>
+        <v>353000</v>
       </c>
       <c r="Z2" t="n">
-        <v>434000</v>
+        <v>353000</v>
       </c>
       <c r="AA2" t="n">
-        <v>87426000</v>
+        <v>121033000</v>
       </c>
       <c r="AB2" t="n">
-        <v>16102000</v>
+        <v>7885000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3177000</v>
+        <v>6487000</v>
       </c>
       <c r="AD2" t="n">
-        <v>68147000</v>
+        <v>106661000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2002596000</v>
+        <v>3047005000</v>
       </c>
       <c r="AF2" t="n">
-        <v>165469000</v>
+        <v>316424000</v>
       </c>
       <c r="AG2" t="n">
-        <v>6554000</v>
+        <v>6685000</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -1653,119 +1653,119 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>158915000</v>
+        <v>309739000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-689140000</v>
+        <v>-804954000</v>
       </c>
       <c r="AL2" t="n">
-        <v>848055000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+        <v>1114693000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>45655000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>309739000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>568819000</v>
+        <v>708811000</v>
       </c>
       <c r="AP2" t="n">
-        <v>210145000</v>
+        <v>261353000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>69091000</v>
+        <v>98874000</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1837127000</v>
+        <v>2730581000</v>
       </c>
       <c r="AT2" t="n">
-        <v>8756000</v>
+        <v>6352000</v>
       </c>
       <c r="AU2" t="n">
-        <v>259457000</v>
+        <v>341144000</v>
       </c>
       <c r="AV2" t="n">
-        <v>174719000</v>
+        <v>257552000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2258000</v>
+        <v>69740000</v>
       </c>
       <c r="AX2" t="n">
-        <v>82480000</v>
+        <v>13852000</v>
       </c>
       <c r="AY2" t="n">
-        <v>848000</v>
+        <v>-42237000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16441000</v>
+        <v>22332000</v>
       </c>
       <c r="BA2" t="n">
-        <v>585672000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-52896000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>638568000</v>
-      </c>
+        <v>583157000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>965953000</v>
+        <v>1819833000</v>
       </c>
       <c r="BE2" t="n">
-        <v>965953000</v>
+        <v>1819833000</v>
       </c>
       <c r="BF2" t="n">
-        <v>965953000</v>
+        <v>1819833000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2341700281</v>
+        <v>2341700000</v>
       </c>
       <c r="C3" t="n">
-        <v>2341700281</v>
+        <v>2341700000</v>
       </c>
       <c r="D3" t="n">
-        <v>1020000</v>
+        <v>1391000</v>
       </c>
       <c r="E3" t="n">
-        <v>2064374000</v>
+        <v>2287821000</v>
       </c>
       <c r="F3" t="n">
-        <v>2064374000</v>
+        <v>2287821000</v>
       </c>
       <c r="G3" t="n">
-        <v>1823383000</v>
+        <v>2017629000</v>
       </c>
       <c r="H3" t="n">
-        <v>2064374000</v>
+        <v>2287821000</v>
       </c>
       <c r="I3" t="n">
-        <v>1020000</v>
+        <v>1391000</v>
       </c>
       <c r="J3" t="n">
-        <v>2064374000</v>
+        <v>2287821000</v>
       </c>
       <c r="K3" t="n">
-        <v>2064374000</v>
+        <v>2287821000</v>
       </c>
       <c r="L3" t="n">
-        <v>2044156000</v>
+        <v>2276436000</v>
       </c>
       <c r="M3" t="n">
-        <v>-20218000</v>
+        <v>-11385000</v>
       </c>
       <c r="N3" t="n">
-        <v>2064374000</v>
+        <v>2287821000</v>
       </c>
       <c r="O3" t="n">
-        <v>9568000</v>
+        <v>959000</v>
       </c>
       <c r="P3" t="n">
-        <v>-746598000</v>
+        <v>-552699000</v>
       </c>
       <c r="Q3" t="n">
         <v>2093306000</v>
@@ -1777,46 +1777,46 @@
         <v>234170000</v>
       </c>
       <c r="T3" t="n">
-        <v>109547000</v>
+        <v>133194000</v>
       </c>
       <c r="U3" t="n">
-        <v>629000</v>
+        <v>1020000</v>
       </c>
       <c r="V3" t="n">
-        <v>629000</v>
+        <v>1020000</v>
       </c>
       <c r="W3" t="n">
-        <v>629000</v>
+        <v>1020000</v>
       </c>
       <c r="X3" t="n">
-        <v>108918000</v>
+        <v>132174000</v>
       </c>
       <c r="Y3" t="n">
-        <v>391000</v>
+        <v>371000</v>
       </c>
       <c r="Z3" t="n">
-        <v>391000</v>
+        <v>371000</v>
       </c>
       <c r="AA3" t="n">
-        <v>91950000</v>
+        <v>95167000</v>
       </c>
       <c r="AB3" t="n">
-        <v>14744000</v>
+        <v>7908000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2414000</v>
+        <v>2628000</v>
       </c>
       <c r="AD3" t="n">
-        <v>74792000</v>
+        <v>84631000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2153703000</v>
+        <v>2409630000</v>
       </c>
       <c r="AF3" t="n">
-        <v>221402000</v>
+        <v>259827000</v>
       </c>
       <c r="AG3" t="n">
-        <v>7273000</v>
+        <v>6813000</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1825,121 +1825,123 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>214129000</v>
+        <v>253014000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-664090000</v>
+        <v>-750804000</v>
       </c>
       <c r="AL3" t="n">
-        <v>878219000</v>
+        <v>1003818000</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>253014000</v>
+      </c>
       <c r="AO3" t="n">
-        <v>581571000</v>
+        <v>676950000</v>
       </c>
       <c r="AP3" t="n">
-        <v>215054000</v>
+        <v>239420000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>81594000</v>
+        <v>87448000</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1932301000</v>
+        <v>2149803000</v>
       </c>
       <c r="AT3" t="n">
-        <v>5281000</v>
+        <v>13065000</v>
       </c>
       <c r="AU3" t="n">
-        <v>203068000</v>
+        <v>191410000</v>
       </c>
       <c r="AV3" t="n">
-        <v>192927000</v>
+        <v>120921000</v>
       </c>
       <c r="AW3" t="n">
-        <v>5511000</v>
+        <v>60343000</v>
       </c>
       <c r="AX3" t="n">
-        <v>4630000</v>
+        <v>10146000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1347000</v>
+        <v>985000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4543000</v>
+        <v>15277000</v>
       </c>
       <c r="BA3" t="n">
-        <v>418613000</v>
+        <v>476680000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-58266000</v>
+        <v>-54133000</v>
       </c>
       <c r="BC3" t="n">
-        <v>476879000</v>
+        <v>530813000</v>
       </c>
       <c r="BD3" t="n">
-        <v>1299449000</v>
+        <v>1452386000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1299449000</v>
+        <v>1452386000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1299449000</v>
+        <v>1452386000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2341700000</v>
+        <v>2341700281</v>
       </c>
       <c r="C4" t="n">
-        <v>2341700000</v>
+        <v>2341700281</v>
       </c>
       <c r="D4" t="n">
-        <v>1391000</v>
+        <v>1020000</v>
       </c>
       <c r="E4" t="n">
-        <v>2287821000</v>
+        <v>2064374000</v>
       </c>
       <c r="F4" t="n">
-        <v>2287821000</v>
+        <v>2064374000</v>
       </c>
       <c r="G4" t="n">
-        <v>2017629000</v>
+        <v>1823383000</v>
       </c>
       <c r="H4" t="n">
-        <v>2287821000</v>
+        <v>2064374000</v>
       </c>
       <c r="I4" t="n">
-        <v>1391000</v>
+        <v>1020000</v>
       </c>
       <c r="J4" t="n">
-        <v>2287821000</v>
+        <v>2064374000</v>
       </c>
       <c r="K4" t="n">
-        <v>2287821000</v>
+        <v>2064374000</v>
       </c>
       <c r="L4" t="n">
-        <v>2276436000</v>
+        <v>2044156000</v>
       </c>
       <c r="M4" t="n">
-        <v>-11385000</v>
+        <v>-20218000</v>
       </c>
       <c r="N4" t="n">
-        <v>2287821000</v>
+        <v>2064374000</v>
       </c>
       <c r="O4" t="n">
-        <v>959000</v>
+        <v>9568000</v>
       </c>
       <c r="P4" t="n">
-        <v>-552699000</v>
+        <v>-746598000</v>
       </c>
       <c r="Q4" t="n">
         <v>2093306000</v>
@@ -1951,46 +1953,46 @@
         <v>234170000</v>
       </c>
       <c r="T4" t="n">
-        <v>133194000</v>
+        <v>109547000</v>
       </c>
       <c r="U4" t="n">
-        <v>1020000</v>
+        <v>629000</v>
       </c>
       <c r="V4" t="n">
-        <v>1020000</v>
+        <v>629000</v>
       </c>
       <c r="W4" t="n">
-        <v>1020000</v>
+        <v>629000</v>
       </c>
       <c r="X4" t="n">
-        <v>132174000</v>
+        <v>108918000</v>
       </c>
       <c r="Y4" t="n">
-        <v>371000</v>
+        <v>391000</v>
       </c>
       <c r="Z4" t="n">
-        <v>371000</v>
+        <v>391000</v>
       </c>
       <c r="AA4" t="n">
-        <v>95167000</v>
+        <v>91950000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7908000</v>
+        <v>14744000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2628000</v>
+        <v>2414000</v>
       </c>
       <c r="AD4" t="n">
-        <v>84631000</v>
+        <v>74792000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2409630000</v>
+        <v>2153703000</v>
       </c>
       <c r="AF4" t="n">
-        <v>259827000</v>
+        <v>221402000</v>
       </c>
       <c r="AG4" t="n">
-        <v>6813000</v>
+        <v>7273000</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1999,121 +2001,119 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>253014000</v>
+        <v>214129000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-750804000</v>
+        <v>-664090000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1003818000</v>
+        <v>878219000</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
-      <c r="AN4" t="n">
-        <v>253014000</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>676950000</v>
+        <v>581571000</v>
       </c>
       <c r="AP4" t="n">
-        <v>239420000</v>
+        <v>215054000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>87448000</v>
+        <v>81594000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2149803000</v>
+        <v>1932301000</v>
       </c>
       <c r="AT4" t="n">
-        <v>13065000</v>
+        <v>5281000</v>
       </c>
       <c r="AU4" t="n">
-        <v>191410000</v>
+        <v>203068000</v>
       </c>
       <c r="AV4" t="n">
-        <v>120921000</v>
+        <v>192927000</v>
       </c>
       <c r="AW4" t="n">
-        <v>60343000</v>
+        <v>5511000</v>
       </c>
       <c r="AX4" t="n">
-        <v>10146000</v>
+        <v>4630000</v>
       </c>
       <c r="AY4" t="n">
-        <v>985000</v>
+        <v>1347000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15277000</v>
+        <v>4543000</v>
       </c>
       <c r="BA4" t="n">
-        <v>476680000</v>
+        <v>418613000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-54133000</v>
+        <v>-58266000</v>
       </c>
       <c r="BC4" t="n">
-        <v>530813000</v>
+        <v>476879000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1452386000</v>
+        <v>1299449000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1452386000</v>
+        <v>1299449000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1452386000</v>
+        <v>1299449000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2341700000</v>
+        <v>2341700281</v>
       </c>
       <c r="C5" t="n">
-        <v>2341700000</v>
+        <v>2341700281</v>
       </c>
       <c r="D5" t="n">
-        <v>1744000</v>
+        <v>664000</v>
       </c>
       <c r="E5" t="n">
-        <v>2881361000</v>
+        <v>1917361000</v>
       </c>
       <c r="F5" t="n">
-        <v>2881361000</v>
+        <v>1917361000</v>
       </c>
       <c r="G5" t="n">
-        <v>2575215000</v>
+        <v>1730138000</v>
       </c>
       <c r="H5" t="n">
-        <v>2881361000</v>
+        <v>1917361000</v>
       </c>
       <c r="I5" t="n">
-        <v>1744000</v>
+        <v>664000</v>
       </c>
       <c r="J5" t="n">
-        <v>2881361000</v>
+        <v>1917361000</v>
       </c>
       <c r="K5" t="n">
-        <v>2881361000</v>
+        <v>1917361000</v>
       </c>
       <c r="L5" t="n">
-        <v>2890248000</v>
+        <v>1895377000</v>
       </c>
       <c r="M5" t="n">
-        <v>8887000</v>
+        <v>-21984000</v>
       </c>
       <c r="N5" t="n">
-        <v>2881361000</v>
+        <v>1917361000</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-179403000</v>
+        <v>-841954000</v>
       </c>
       <c r="Q5" t="n">
         <v>2093306000</v>
@@ -2125,46 +2125,46 @@
         <v>234170000</v>
       </c>
       <c r="T5" t="n">
-        <v>156757000</v>
+        <v>107219000</v>
       </c>
       <c r="U5" t="n">
-        <v>1391000</v>
+        <v>230000</v>
       </c>
       <c r="V5" t="n">
-        <v>1391000</v>
+        <v>230000</v>
       </c>
       <c r="W5" t="n">
-        <v>1391000</v>
+        <v>230000</v>
       </c>
       <c r="X5" t="n">
-        <v>155366000</v>
+        <v>106989000</v>
       </c>
       <c r="Y5" t="n">
-        <v>353000</v>
+        <v>434000</v>
       </c>
       <c r="Z5" t="n">
-        <v>353000</v>
+        <v>434000</v>
       </c>
       <c r="AA5" t="n">
-        <v>121033000</v>
+        <v>87426000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7885000</v>
+        <v>16102000</v>
       </c>
       <c r="AC5" t="n">
-        <v>6487000</v>
+        <v>3177000</v>
       </c>
       <c r="AD5" t="n">
-        <v>106661000</v>
+        <v>68147000</v>
       </c>
       <c r="AE5" t="n">
-        <v>3047005000</v>
+        <v>2002596000</v>
       </c>
       <c r="AF5" t="n">
-        <v>316424000</v>
+        <v>165469000</v>
       </c>
       <c r="AG5" t="n">
-        <v>6685000</v>
+        <v>6554000</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2173,69 +2173,69 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>309739000</v>
+        <v>158915000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-804954000</v>
+        <v>-689140000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1114693000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>45655000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>309739000</v>
-      </c>
+        <v>848055000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>708811000</v>
+        <v>568819000</v>
       </c>
       <c r="AP5" t="n">
-        <v>261353000</v>
+        <v>210145000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>98874000</v>
+        <v>69091000</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2730581000</v>
+        <v>1837127000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6352000</v>
+        <v>8756000</v>
       </c>
       <c r="AU5" t="n">
-        <v>341144000</v>
+        <v>259457000</v>
       </c>
       <c r="AV5" t="n">
-        <v>257552000</v>
+        <v>174719000</v>
       </c>
       <c r="AW5" t="n">
-        <v>69740000</v>
+        <v>2258000</v>
       </c>
       <c r="AX5" t="n">
-        <v>13852000</v>
+        <v>82480000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-42237000</v>
+        <v>848000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22332000</v>
+        <v>16441000</v>
       </c>
       <c r="BA5" t="n">
-        <v>583157000</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
+        <v>585672000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-52896000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>638568000</v>
+      </c>
       <c r="BD5" t="n">
-        <v>1819833000</v>
+        <v>965953000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1819833000</v>
+        <v>965953000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1819833000</v>
+        <v>965953000</v>
       </c>
     </row>
   </sheetData>
@@ -2406,374 +2406,374 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-312754000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>24854000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-90204000</v>
+      </c>
       <c r="D2" t="n">
-        <v>965953000</v>
+        <v>1819833000</v>
       </c>
       <c r="E2" t="n">
-        <v>1299449000</v>
+        <v>1740255000</v>
       </c>
       <c r="F2" t="n">
-        <v>-22839000</v>
+        <v>49699000</v>
       </c>
       <c r="G2" t="n">
-        <v>-310657000</v>
+        <v>29879000</v>
       </c>
       <c r="H2" t="n">
-        <v>-443000</v>
+        <v>-1270000</v>
       </c>
       <c r="I2" t="n">
-        <v>-42000</v>
+        <v>-455000</v>
       </c>
       <c r="J2" t="n">
-        <v>2540000</v>
+        <v>-83909000</v>
       </c>
       <c r="K2" t="n">
-        <v>2007000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
+        <v>5856000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>533000</v>
+        <v>-89765000</v>
       </c>
       <c r="O2" t="n">
-        <v>533000</v>
+        <v>439000</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-90204000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-312754000</v>
+        <v>115058000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-6170000</v>
       </c>
       <c r="S2" t="n">
-        <v>-265442000</v>
+        <v>38575000</v>
       </c>
       <c r="T2" t="n">
-        <v>2689000</v>
+        <v>-23037000</v>
       </c>
       <c r="U2" t="n">
-        <v>-3051000</v>
+        <v>31407000</v>
       </c>
       <c r="V2" t="n">
-        <v>-3620000</v>
+        <v>100907000</v>
       </c>
       <c r="W2" t="n">
-        <v>-75872000</v>
+        <v>-8526000</v>
       </c>
       <c r="X2" t="n">
-        <v>-185588000</v>
+        <v>-62176000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1965000</v>
+        <v>-5565000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>29174000</v>
+        <v>35638000</v>
       </c>
       <c r="AB2" t="n">
-        <v>29174000</v>
+        <v>35638000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-294000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
+        <v>-327000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-106577000</v>
+        <v>28083000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-169794000</v>
+        <v>-237452000</v>
       </c>
       <c r="C3" t="n">
-        <v>-18000</v>
+        <v>-6957000</v>
       </c>
       <c r="D3" t="n">
-        <v>1299449000</v>
+        <v>1452386000</v>
       </c>
       <c r="E3" t="n">
-        <v>1452386000</v>
+        <v>1819833000</v>
       </c>
       <c r="F3" t="n">
-        <v>-18086000</v>
+        <v>-135246000</v>
       </c>
       <c r="G3" t="n">
-        <v>-134851000</v>
+        <v>-232201000</v>
       </c>
       <c r="H3" t="n">
-        <v>-680000</v>
+        <v>-650000</v>
       </c>
       <c r="I3" t="n">
-        <v>-309000</v>
+        <v>-297000</v>
       </c>
       <c r="J3" t="n">
-        <v>35605000</v>
+        <v>-1056000</v>
       </c>
       <c r="K3" t="n">
-        <v>2862000</v>
+        <v>4872000</v>
       </c>
       <c r="L3" t="n">
-        <v>32761000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>32761000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-18000</v>
+        <v>-5928000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1029000</v>
       </c>
       <c r="P3" t="n">
-        <v>-18000</v>
+        <v>-6957000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-169776000</v>
+        <v>-230495000</v>
       </c>
       <c r="R3" t="n">
-        <v>-129000</v>
+        <v>-4891000</v>
       </c>
       <c r="S3" t="n">
-        <v>-64430000</v>
+        <v>116400000</v>
       </c>
       <c r="T3" t="n">
-        <v>-11446000</v>
+        <v>3997000</v>
       </c>
       <c r="U3" t="n">
-        <v>13757000</v>
+        <v>-14529000</v>
       </c>
       <c r="V3" t="n">
-        <v>7648000</v>
+        <v>-7542000</v>
       </c>
       <c r="W3" t="n">
-        <v>-82872000</v>
+        <v>125792000</v>
       </c>
       <c r="X3" t="n">
-        <v>8483000</v>
+        <v>8682000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2553000</v>
+        <v>-4575000</v>
       </c>
       <c r="Z3" t="n">
-        <v>9060000</v>
+        <v>959000</v>
       </c>
       <c r="AA3" t="n">
-        <v>33898000</v>
+        <v>38295000</v>
       </c>
       <c r="AB3" t="n">
-        <v>33898000</v>
+        <v>38295000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-397000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-5719000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-210165000</v>
+        <v>-391946000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-237452000</v>
+        <v>-169794000</v>
       </c>
       <c r="C4" t="n">
-        <v>-6957000</v>
+        <v>-18000</v>
       </c>
       <c r="D4" t="n">
+        <v>1299449000</v>
+      </c>
+      <c r="E4" t="n">
         <v>1452386000</v>
       </c>
-      <c r="E4" t="n">
-        <v>1819833000</v>
-      </c>
       <c r="F4" t="n">
-        <v>-135246000</v>
+        <v>-18086000</v>
       </c>
       <c r="G4" t="n">
-        <v>-232201000</v>
+        <v>-134851000</v>
       </c>
       <c r="H4" t="n">
-        <v>-650000</v>
+        <v>-680000</v>
       </c>
       <c r="I4" t="n">
-        <v>-297000</v>
+        <v>-309000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1056000</v>
+        <v>35605000</v>
       </c>
       <c r="K4" t="n">
-        <v>4872000</v>
+        <v>2862000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>32761000</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>32761000</v>
       </c>
       <c r="N4" t="n">
-        <v>-5928000</v>
+        <v>-18000</v>
       </c>
       <c r="O4" t="n">
-        <v>1029000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-6957000</v>
+        <v>-18000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-230495000</v>
+        <v>-169776000</v>
       </c>
       <c r="R4" t="n">
-        <v>-4891000</v>
+        <v>-129000</v>
       </c>
       <c r="S4" t="n">
-        <v>116400000</v>
+        <v>-64430000</v>
       </c>
       <c r="T4" t="n">
-        <v>3997000</v>
+        <v>-11446000</v>
       </c>
       <c r="U4" t="n">
-        <v>-14529000</v>
+        <v>13757000</v>
       </c>
       <c r="V4" t="n">
-        <v>-7542000</v>
+        <v>7648000</v>
       </c>
       <c r="W4" t="n">
-        <v>125792000</v>
+        <v>-82872000</v>
       </c>
       <c r="X4" t="n">
-        <v>8682000</v>
+        <v>8483000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-4575000</v>
+        <v>-2553000</v>
       </c>
       <c r="Z4" t="n">
-        <v>959000</v>
+        <v>9060000</v>
       </c>
       <c r="AA4" t="n">
-        <v>38295000</v>
+        <v>33898000</v>
       </c>
       <c r="AB4" t="n">
-        <v>38295000</v>
+        <v>33898000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-397000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-5719000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-391946000</v>
+        <v>-210165000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>24854000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-90204000</v>
-      </c>
+        <v>-312754000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>1819833000</v>
+        <v>965953000</v>
       </c>
       <c r="E5" t="n">
-        <v>1740255000</v>
+        <v>1299449000</v>
       </c>
       <c r="F5" t="n">
-        <v>49699000</v>
+        <v>-22839000</v>
       </c>
       <c r="G5" t="n">
-        <v>29879000</v>
+        <v>-310657000</v>
       </c>
       <c r="H5" t="n">
-        <v>-1270000</v>
+        <v>-443000</v>
       </c>
       <c r="I5" t="n">
-        <v>-455000</v>
+        <v>-42000</v>
       </c>
       <c r="J5" t="n">
-        <v>-83909000</v>
+        <v>2540000</v>
       </c>
       <c r="K5" t="n">
-        <v>5856000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>2007000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>-89765000</v>
+        <v>533000</v>
       </c>
       <c r="O5" t="n">
-        <v>439000</v>
+        <v>533000</v>
       </c>
       <c r="P5" t="n">
-        <v>-90204000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>115058000</v>
+        <v>-312754000</v>
       </c>
       <c r="R5" t="n">
-        <v>-6170000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>38575000</v>
+        <v>-265442000</v>
       </c>
       <c r="T5" t="n">
-        <v>-23037000</v>
+        <v>2689000</v>
       </c>
       <c r="U5" t="n">
-        <v>31407000</v>
+        <v>-3051000</v>
       </c>
       <c r="V5" t="n">
-        <v>100907000</v>
+        <v>-3620000</v>
       </c>
       <c r="W5" t="n">
-        <v>-8526000</v>
+        <v>-75872000</v>
       </c>
       <c r="X5" t="n">
-        <v>-62176000</v>
+        <v>-185588000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-5565000</v>
+        <v>-1965000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>35638000</v>
+        <v>29174000</v>
       </c>
       <c r="AB5" t="n">
-        <v>35638000</v>
+        <v>29174000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-327000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-294000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
       <c r="AE5" t="n">
-        <v>28083000</v>
+        <v>-106577000</v>
       </c>
     </row>
   </sheetData>
@@ -3313,182 +3313,182 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3634,7 +3634,7 @@
         <v>2.41</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="AH2" t="n">
         <v>48565212</v>
@@ -3670,10 +3670,10 @@
         <v>1953315196</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.385</v>
+        <v>0.66</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.91</v>
+        <v>0.72</v>
       </c>
       <c r="AU2" t="n">
         <v>4.09537</v>
@@ -3753,10 +3753,10 @@
         <v>-10.943</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.77215195</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.017029</v>
@@ -3871,132 +3871,132 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>CHINA RAREEARTH</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>finmb_4493418</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.03999996</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.060606</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.66 - 0.72</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.02000004</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.027777834</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1756378740</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1756728000</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ED2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DC2" t="n">
+      <c r="EE2" t="n">
         <v>1750225444</v>
       </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1756378740</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>1756728000</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>finmb_4493418</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
         <v>946949400000</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="inlineStr">
         <is>
           <t>0.66 - 0.72</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.8181818</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>0.385 - 0.91</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.21000004</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.23076926</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>77.21519499999999</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>CHINA RAREEARTH</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
